--- a/data/trans_orig/P57_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57_R-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2016</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106306</t>
+          <t>104768</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>148148</t>
+          <t>147247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137347</t>
+          <t>139034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181629</t>
+          <t>183459</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>254922</t>
+          <t>259422</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>321567</t>
+          <t>317738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>521345</t>
+          <t>522246</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>563187</t>
+          <t>564725</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>485765</t>
+          <t>483935</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>530047</t>
+          <t>528360</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1015320</t>
+          <t>1019149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1081965</t>
+          <t>1077465</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>180937</t>
+          <t>180112</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>230121</t>
+          <t>231454</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>219883</t>
+          <t>222043</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>278460</t>
+          <t>279381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>415347</t>
+          <t>417421</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>493977</t>
+          <t>492102</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>791208</t>
+          <t>789875</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>840392</t>
+          <t>841217</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>763476</t>
+          <t>762555</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>822053</t>
+          <t>819893</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1569288</t>
+          <t>1571163</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1647918</t>
+          <t>1645844</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,77%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111369</t>
+          <t>110366</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155181</t>
+          <t>153406</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130705</t>
+          <t>129265</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177105</t>
+          <t>173984</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>253622</t>
+          <t>252525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>315437</t>
+          <t>317644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>601258</t>
+          <t>603033</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645070</t>
+          <t>646073</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>602200</t>
+          <t>605321</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>648600</t>
+          <t>650040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1220307</t>
+          <t>1218100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1282122</t>
+          <t>1283219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140782</t>
+          <t>142035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187229</t>
+          <t>189120</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>237290</t>
+          <t>235606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>297506</t>
+          <t>296078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>395965</t>
+          <t>390532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>468633</t>
+          <t>468008</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>746244</t>
+          <t>744353</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>792691</t>
+          <t>791438</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>741961</t>
+          <t>743389</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>802177</t>
+          <t>803861</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1504307</t>
+          <t>1504932</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1576975</t>
+          <t>1582408</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>580009</t>
+          <t>583378</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>668542</t>
+          <t>673888</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>780032</t>
+          <t>774090</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>882980</t>
+          <t>877276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1386274</t>
+          <t>1388120</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1529294</t>
+          <t>1525323</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2712191</t>
+          <t>2706845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2800724</t>
+          <t>2797355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2645124</t>
+          <t>2650828</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2748072</t>
+          <t>2754014</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5379543</t>
+          <t>5383514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5522563</t>
+          <t>5520717</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2023</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85708</t>
+          <t>83971</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119313</t>
+          <t>120246</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115388</t>
+          <t>114335</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146435</t>
+          <t>144793</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>209942</t>
+          <t>208274</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>256360</t>
+          <t>254031</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>509306</t>
+          <t>508373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>542911</t>
+          <t>544648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>523801</t>
+          <t>525443</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>554848</t>
+          <t>555901</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1042495</t>
+          <t>1044824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1088913</t>
+          <t>1090581</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60488</t>
+          <t>55219</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>152794</t>
+          <t>152915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145263</t>
+          <t>145304</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>181504</t>
+          <t>182315</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>181872</t>
+          <t>174612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>320962</t>
+          <t>323283</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1038721</t>
+          <t>1038600</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1131027</t>
+          <t>1136296</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>768251</t>
+          <t>767440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>804492</t>
+          <t>804451</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1820308</t>
+          <t>1817987</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1959398</t>
+          <t>1966658</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47118</t>
+          <t>48741</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81305</t>
+          <t>80547</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31758</t>
+          <t>34993</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96077</t>
+          <t>93511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83852</t>
+          <t>83345</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>165977</t>
+          <t>161039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623375</t>
+          <t>624133</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657562</t>
+          <t>655939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>833418</t>
+          <t>835984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>897737</t>
+          <t>894502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1468199</t>
+          <t>1473137</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1550324</t>
+          <t>1550831</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129601</t>
+          <t>129061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>173985</t>
+          <t>172269</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>171277</t>
+          <t>169818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>241146</t>
+          <t>238123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>319367</t>
+          <t>320609</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>397310</t>
+          <t>396770</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>750834</t>
+          <t>752550</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>795218</t>
+          <t>795758</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>849684</t>
+          <t>852707</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>919553</t>
+          <t>921012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1618339</t>
+          <t>1618879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1696282</t>
+          <t>1695040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>337766</t>
+          <t>331725</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>478937</t>
+          <t>479683</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>467756</t>
+          <t>460815</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>632423</t>
+          <t>630378</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>872095</t>
+          <t>887320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1086800</t>
+          <t>1086718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2970696</t>
+          <t>2969950</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3111867</t>
+          <t>3117908</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3007893</t>
+          <t>3009938</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3172560</t>
+          <t>3179501</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6003149</t>
+          <t>6003231</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6217854</t>
+          <t>6202629</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57_R-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104768</t>
+          <t>108387</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147247</t>
+          <t>148968</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139034</t>
+          <t>139259</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>183459</t>
+          <t>184211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>259422</t>
+          <t>257015</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>317738</t>
+          <t>313325</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>522246</t>
+          <t>520525</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>564725</t>
+          <t>561106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>483935</t>
+          <t>483183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>528360</t>
+          <t>528135</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1019149</t>
+          <t>1023562</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1077465</t>
+          <t>1079872</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,78%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>180112</t>
+          <t>180715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>231454</t>
+          <t>232074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>222043</t>
+          <t>219670</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>279381</t>
+          <t>278249</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>417421</t>
+          <t>414835</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>492102</t>
+          <t>491302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>789875</t>
+          <t>789255</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>841217</t>
+          <t>840614</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>762555</t>
+          <t>763687</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>819893</t>
+          <t>822266</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1571163</t>
+          <t>1571963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1645844</t>
+          <t>1648430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,89%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110366</t>
+          <t>111224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153406</t>
+          <t>152983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129265</t>
+          <t>129919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>173984</t>
+          <t>174856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>252525</t>
+          <t>250888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>317644</t>
+          <t>317640</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>603033</t>
+          <t>603456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>646073</t>
+          <t>645215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>605321</t>
+          <t>604449</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>650040</t>
+          <t>649386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1218100</t>
+          <t>1218104</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1283219</t>
+          <t>1284856</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142035</t>
+          <t>142791</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189120</t>
+          <t>186262</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>235606</t>
+          <t>237805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>296078</t>
+          <t>298556</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>390532</t>
+          <t>393325</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>468008</t>
+          <t>468370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>744353</t>
+          <t>747211</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>791438</t>
+          <t>790682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>743389</t>
+          <t>740911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>803861</t>
+          <t>801662</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1504932</t>
+          <t>1504570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1582408</t>
+          <t>1579615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>583378</t>
+          <t>584516</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>673888</t>
+          <t>679576</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>774090</t>
+          <t>777164</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>877276</t>
+          <t>880662</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1388120</t>
+          <t>1388057</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1525323</t>
+          <t>1525720</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2706845</t>
+          <t>2701157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2797355</t>
+          <t>2796217</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2650828</t>
+          <t>2647442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2754014</t>
+          <t>2750940</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5383514</t>
+          <t>5383117</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5520717</t>
+          <t>5520780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2673,32 +2673,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>102552</t>
+          <t>108359</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83971</t>
+          <t>91185</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120246</t>
+          <t>127834</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2708,32 +2708,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>129235</t>
+          <t>140409</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114335</t>
+          <t>124383</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144793</t>
+          <t>158246</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2743,22 +2743,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>231787</t>
+          <t>248768</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226223</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>254031</t>
+          <t>272858</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>526067</t>
+          <t>574958</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>508373</t>
+          <t>555483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>544648</t>
+          <t>592132</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2821,32 +2821,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>541001</t>
+          <t>586434</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>525443</t>
+          <t>568597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>555901</t>
+          <t>602460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2856,27 +2856,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1067068</t>
+          <t>1161391</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1044824</t>
+          <t>1137301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1090581</t>
+          <t>1183936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>628619</t>
+          <t>683317</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>628619</t>
+          <t>683317</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>628619</t>
+          <t>683317</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>670236</t>
+          <t>726843</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>670236</t>
+          <t>726843</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>670236</t>
+          <t>726843</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1298855</t>
+          <t>1410159</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1298855</t>
+          <t>1410159</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1298855</t>
+          <t>1410159</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>114896</t>
+          <t>126606</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55219</t>
+          <t>108422</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>152915</t>
+          <t>151473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>162421</t>
+          <t>184323</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145304</t>
+          <t>164061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182315</t>
+          <t>204705</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>277317</t>
+          <t>310929</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174612</t>
+          <t>282312</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>323283</t>
+          <t>343059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -3129,32 +3129,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1076619</t>
+          <t>920831</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1038600</t>
+          <t>895964</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1136296</t>
+          <t>939015</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>787334</t>
+          <t>878725</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>767440</t>
+          <t>858343</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>804451</t>
+          <t>898987</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3199,32 +3199,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1863953</t>
+          <t>1799557</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1817987</t>
+          <t>1767427</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1966658</t>
+          <t>1828174</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3242,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191515</t>
+          <t>1047437</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191515</t>
+          <t>1047437</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191515</t>
+          <t>1047437</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>949755</t>
+          <t>1063048</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>949755</t>
+          <t>1063048</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>949755</t>
+          <t>1063048</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3312,17 +3312,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2141270</t>
+          <t>2110486</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2141270</t>
+          <t>2110486</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2141270</t>
+          <t>2110486</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3359,32 +3359,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62693</t>
+          <t>72473</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48741</t>
+          <t>57833</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80547</t>
+          <t>92060</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3394,32 +3394,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>69111</t>
+          <t>82627</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34993</t>
+          <t>67171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93511</t>
+          <t>98825</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3429,32 +3429,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>131805</t>
+          <t>155100</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83345</t>
+          <t>133385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161039</t>
+          <t>179437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -3472,32 +3472,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>641987</t>
+          <t>730600</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624133</t>
+          <t>711013</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655939</t>
+          <t>745240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3507,32 +3507,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>860384</t>
+          <t>725438</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>835984</t>
+          <t>709240</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>894502</t>
+          <t>740894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1502371</t>
+          <t>1456038</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1473137</t>
+          <t>1431701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1550831</t>
+          <t>1477753</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3620,17 +3620,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>929495</t>
+          <t>808065</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>929495</t>
+          <t>808065</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>929495</t>
+          <t>808065</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634176</t>
+          <t>1611138</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634176</t>
+          <t>1611138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634176</t>
+          <t>1611138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3702,32 +3702,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>149735</t>
+          <t>164368</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129061</t>
+          <t>142442</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172269</t>
+          <t>188468</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>213083</t>
+          <t>234599</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>169818</t>
+          <t>210997</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>238123</t>
+          <t>258353</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3772,32 +3772,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>362817</t>
+          <t>398967</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>320609</t>
+          <t>365342</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>396770</t>
+          <t>430229</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -3815,32 +3815,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>775084</t>
+          <t>823598</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>752550</t>
+          <t>799498</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>795758</t>
+          <t>845524</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>877747</t>
+          <t>880163</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>852707</t>
+          <t>856409</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>921012</t>
+          <t>903765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3885,32 +3885,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1652832</t>
+          <t>1703761</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1618879</t>
+          <t>1672499</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1695040</t>
+          <t>1737386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -3928,17 +3928,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>924819</t>
+          <t>987966</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>924819</t>
+          <t>987966</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>924819</t>
+          <t>987966</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1090830</t>
+          <t>1114762</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1090830</t>
+          <t>1114762</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1090830</t>
+          <t>1114762</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3998,17 +3998,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2015649</t>
+          <t>2102728</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2015649</t>
+          <t>2102728</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2015649</t>
+          <t>2102728</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4045,32 +4045,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>429876</t>
+          <t>471807</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>331725</t>
+          <t>430826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>479683</t>
+          <t>514378</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>573850</t>
+          <t>641958</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>460815</t>
+          <t>599754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>630378</t>
+          <t>677803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4115,32 +4115,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1003726</t>
+          <t>1113764</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>887320</t>
+          <t>1061579</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1086718</t>
+          <t>1174508</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4158,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3019757</t>
+          <t>3049986</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2969950</t>
+          <t>3007415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3117908</t>
+          <t>3090967</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3066466</t>
+          <t>3070760</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3009938</t>
+          <t>3034915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3179501</t>
+          <t>3112964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4228,32 +4228,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6086223</t>
+          <t>6120747</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6003231</t>
+          <t>6060003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6202629</t>
+          <t>6172932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -4271,17 +4271,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4306,17 +4306,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
